--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536138_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536138_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,28 +641,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7785</v>
+        <v>7.3935</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7407</v>
+        <v>4.3557</v>
       </c>
       <c r="F3" t="n">
         <v>3.0378</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8655</v>
+        <v>2.4805</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5188</v>
+        <v>2.1339</v>
       </c>
       <c r="I3" t="n">
         <v>0.3466</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1752</v>
+        <v>1.7902</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7057</v>
+        <v>1.3207</v>
       </c>
       <c r="L3" t="n">
         <v>0.4695</v>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>V. MUNOZ QUINONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.615</v>
+        <v>-0.2725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.615</v>
+        <v>-0.9459</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.6734</v>
       </c>
       <c r="G6" t="n">
-        <v>0.615</v>
+        <v>-2.9443</v>
       </c>
       <c r="H6" t="n">
-        <v>0.615</v>
+        <v>-0.4624</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-2.4819</v>
       </c>
       <c r="J6" t="n">
-        <v>0.615</v>
+        <v>-2.2145</v>
       </c>
       <c r="K6" t="n">
-        <v>0.615</v>
+        <v>-0.9345</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.7298</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.4721</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.2019</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9749</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.195</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.7553</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2435</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.5118</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9415</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. MUNOZ QUINONES</t>
+          <t>F. TORREBLANCA CATALAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2725</v>
+        <v>-0.8647</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9459</v>
+        <v>-0.0163</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6734</v>
+        <v>-0.8485</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9443</v>
+        <v>-1.1176</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4624</v>
+        <v>-0.4357</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4819</v>
+        <v>-0.6819</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2145</v>
+        <v>-0.1695</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9345</v>
+        <v>0.3895</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.28</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7298</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4721</v>
+        <v>-0.8252</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2019</v>
+        <v>-0.1229</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9749</v>
+        <v>0.39</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1699</v>
+        <v>0.585</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7553</v>
+        <v>-0.1371</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2435</v>
+        <v>0.3482</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5118</v>
+        <v>-0.4853</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9415</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. TORREBLANCA CATALAN</t>
+          <t>P. GARCIA CARRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8647</v>
+        <v>-0.8903</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0163</v>
+        <v>-2.8571</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8485</v>
+        <v>1.9667</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1176</v>
+        <v>3.3125</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4357</v>
+        <v>3.2249</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6819</v>
+        <v>0.0876</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1695</v>
+        <v>1.6762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3895</v>
+        <v>1.5952</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9481000000000001</v>
+        <v>1.6364</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8252</v>
+        <v>1.6298</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1229</v>
+        <v>0.0066</v>
       </c>
       <c r="P8" t="n">
-        <v>0.39</v>
+        <v>-2.7298</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.195</v>
+        <v>-3.8997</v>
       </c>
       <c r="R8" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1371</v>
+        <v>0.4629</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3482</v>
+        <v>-0.1962</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4853</v>
+        <v>0.6591</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.9359</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.4373</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GARCIA CARRERO</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8903</v>
+        <v>-1.8837</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8571</v>
+        <v>-3.3413</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9667</v>
+        <v>1.4576</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3125</v>
+        <v>1.2997</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2249</v>
+        <v>-0.1339</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0876</v>
+        <v>1.4336</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6762</v>
+        <v>0.2046</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5952</v>
+        <v>-0.8075</v>
       </c>
       <c r="L9" t="n">
-        <v>0.081</v>
+        <v>1.0121</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6364</v>
+        <v>1.0951</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6298</v>
+        <v>0.6736</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0066</v>
+        <v>0.4215</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7298</v>
+        <v>-2.1448</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.8997</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1699</v>
+        <v>1.7549</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4629</v>
+        <v>0.5659</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1962</v>
+        <v>0.7382</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6591</v>
+        <v>-0.1723</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.9359</v>
+        <v>-1.6045</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4373</v>
+        <v>-0.3844</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4986</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,64 +1222,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8837</v>
+        <v>-3.4249</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3413</v>
+        <v>-2.5214</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4576</v>
+        <v>-0.9036</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2997</v>
+        <v>-0.8714</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1339</v>
+        <v>-0.3707</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4336</v>
+        <v>-0.5006</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2046</v>
+        <v>-0.599</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8075</v>
+        <v>0.041</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0121</v>
+        <v>-0.64</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0951</v>
+        <v>-0.2724</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6736</v>
+        <v>-0.4118</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4215</v>
+        <v>0.1394</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1448</v>
+        <v>-1.7549</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8997</v>
+        <v>-1.9499</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7549</v>
+        <v>0.195</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5659</v>
+        <v>0.4213</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7382</v>
+        <v>0.0275</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1723</v>
+        <v>0.3938</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6045</v>
+        <v>-1.2201</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3844</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2201</v>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>I. CORRALIZA COBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,64 +1305,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4249</v>
+        <v>-3.4529</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5214</v>
+        <v>-2.2904</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9036</v>
+        <v>-1.1625</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8714</v>
+        <v>-1.7354</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3707</v>
+        <v>-0.4135</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5006</v>
+        <v>-1.322</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.599</v>
+        <v>-1.535</v>
       </c>
       <c r="K11" t="n">
-        <v>0.041</v>
+        <v>-0.336</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.64</v>
+        <v>-1.199</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2724</v>
+        <v>-0.2004</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4118</v>
+        <v>-0.0775</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1394</v>
+        <v>-0.1229</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7549</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9499</v>
+        <v>-3.1198</v>
       </c>
       <c r="R11" t="n">
-        <v>0.195</v>
+        <v>0.7799</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4213</v>
+        <v>-0.5977</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0275</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3938</v>
+        <v>-0.522</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2201</v>
+        <v>1.2201</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4401</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2201</v>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. CORRALIZA COBA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,157 +1388,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4529</v>
+        <v>15.7523</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2904</v>
+        <v>3.626100000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1625</v>
+        <v>12.126</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7354</v>
+        <v>10.6024</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4135</v>
+        <v>11.2499</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.322</v>
+        <v>-0.6476000000000003</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.535</v>
+        <v>7.128299999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.336</v>
+        <v>6.5465</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.199</v>
+        <v>0.5817999999999997</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2004</v>
+        <v>3.4742</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0775</v>
+        <v>4.7034</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1229</v>
+        <v>-1.2292</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3398</v>
+        <v>-5.849500000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1198</v>
+        <v>-19.4986</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7799</v>
+        <v>13.6491</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5977</v>
+        <v>7.046500000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.07580000000000001</v>
+        <v>5.385999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.522</v>
+        <v>1.6602</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2201</v>
+        <v>3.952600000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4401</v>
+        <v>10.61</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>play_by_play_2536138_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-6.6576</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. WALTON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.7523</v>
+        <v>3.6198</v>
       </c>
       <c r="E13" t="n">
-        <v>3.626100000000001</v>
+        <v>3.528</v>
       </c>
       <c r="F13" t="n">
-        <v>12.126</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>10.6024</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>11.2498</v>
+        <v>0.0649</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6476000000000001</v>
+        <v>0.5524</v>
       </c>
       <c r="J13" t="n">
-        <v>7.128299999999999</v>
+        <v>1.0277</v>
       </c>
       <c r="K13" t="n">
-        <v>6.546499999999999</v>
+        <v>0.8902</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5817999999999997</v>
+        <v>0.1375</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4742</v>
+        <v>-0.4103</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7034</v>
+        <v>-0.8252</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2292</v>
+        <v>0.4149</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.849500000000001</v>
+        <v>2.3398</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.4986</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6491</v>
+        <v>2.3398</v>
       </c>
       <c r="S13" t="n">
-        <v>7.046500000000002</v>
+        <v>-0.9023</v>
       </c>
       <c r="T13" t="n">
-        <v>5.385999999999999</v>
+        <v>-0.2184</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6602</v>
+        <v>-0.6839</v>
       </c>
       <c r="V13" t="n">
-        <v>3.952600000000001</v>
+        <v>1.5649</v>
       </c>
       <c r="W13" t="n">
-        <v>10.61</v>
+        <v>2.7187</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.6576</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>-1.1538</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2536138_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. WALTON</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,67 +1550,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6198</v>
+        <v>3.1633</v>
       </c>
       <c r="E14" t="n">
-        <v>3.528</v>
+        <v>-0.0814</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09180000000000001</v>
+        <v>3.2447</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6173999999999999</v>
+        <v>2.3688</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0649</v>
+        <v>-0.9152</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5524</v>
+        <v>3.2839</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0277</v>
+        <v>1.6901</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8902</v>
+        <v>-0.91</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1375</v>
+        <v>2.6001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4103</v>
+        <v>0.6786</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8252</v>
+        <v>-0.0052</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4149</v>
+        <v>0.6838</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3398</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.9248</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3398</v>
+        <v>2.9248</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9023</v>
+        <v>-0.757</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2184</v>
+        <v>-0.3453</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6839</v>
+        <v>-0.4117</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5649</v>
+        <v>1.5515</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7187</v>
+        <v>1.4986</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1538</v>
+        <v>0.0529</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>D. KROHNERT MOTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1633</v>
+        <v>2.3947</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0814</v>
+        <v>1.8138</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2447</v>
+        <v>0.5809</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3688</v>
+        <v>0.7961</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9152</v>
+        <v>-0.0803</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2839</v>
+        <v>0.8764</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6901</v>
+        <v>1.6082</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.91</v>
+        <v>0.3366</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6001</v>
+        <v>1.2716</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6786</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0052</v>
+        <v>-0.4169</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6838</v>
+        <v>-0.3951</v>
       </c>
       <c r="P15" t="n">
+        <v>1.3649</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.9248</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.9248</v>
+        <v>1.3649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.757</v>
+        <v>-0.2833</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3453</v>
+        <v>0.2056</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4117</v>
+        <v>-0.4889</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5515</v>
+        <v>0.517</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4986</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0529</v>
+        <v>0.517</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KROHNERT MOTO</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3947</v>
+        <v>0.25</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8138</v>
+        <v>0.7904</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5809</v>
+        <v>-0.5404</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7961</v>
+        <v>-0.4631</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0803</v>
+        <v>0.9191</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8764</v>
+        <v>-1.3822</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6082</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3366</v>
+        <v>1.2671</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2716</v>
+        <v>-2.066</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8120000000000001</v>
+        <v>0.3358</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4169</v>
+        <v>-0.348</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3951</v>
+        <v>0.6838</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3649</v>
+        <v>2.5348</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3649</v>
+        <v>2.5348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2833</v>
+        <v>-0.668</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2056</v>
+        <v>0.3692</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4889</v>
+        <v>-1.0372</v>
       </c>
       <c r="V16" t="n">
-        <v>0.517</v>
+        <v>-1.1538</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X16" t="n">
-        <v>0.517</v>
+        <v>-2.3738</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.215</v>
+        <v>-0.2173</v>
       </c>
       <c r="E17" t="n">
-        <v>1.215</v>
+        <v>-0.4986</v>
       </c>
       <c r="F17" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.4772</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.7494</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.6805</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.6805</v>
+      </c>
+      <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.215</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.215</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.215</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.215</v>
-      </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.2033</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.0689</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.2722</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7799</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.0919</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>J. CHARLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.25</v>
+        <v>-1.3744</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7904</v>
+        <v>-2.2705</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5404</v>
+        <v>0.8961</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4631</v>
+        <v>-0.7793</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9191</v>
+        <v>-0.6936</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3822</v>
+        <v>-0.0857</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.5825</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2671</v>
+        <v>-0.623</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.066</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3358</v>
+        <v>-0.1969</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.348</v>
+        <v>-0.0706</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6838</v>
+        <v>-0.1262</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5348</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q18" t="n">
+        <v>-1.9499</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.5348</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.668</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.3692</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-1.0372</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-1.1538</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3738</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2173</v>
+        <v>-2.2808</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4986</v>
+        <v>-1.5687</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2813</v>
+        <v>-0.7121</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4772</v>
+        <v>-1.9698</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7494</v>
+        <v>-2.0023</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2722</v>
+        <v>0.0325</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6805</v>
+        <v>-0.4099</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6805</v>
+        <v>-1.1064</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.6965</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2033</v>
+        <v>-1.5599</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0689</v>
+        <v>-0.8959</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2722</v>
+        <v>-0.664</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7799</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7799</v>
+        <v>1.1699</v>
       </c>
       <c r="S19" t="n">
-        <v>0.09</v>
+        <v>-0.6052</v>
       </c>
       <c r="T19" t="n">
-        <v>0.182</v>
+        <v>-0.4291</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0919</v>
+        <v>-0.1762</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.61</v>
+        <v>1.0741</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.61</v>
+        <v>-0.146</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CHARLES</t>
+          <t>P. SUAREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3744</v>
+        <v>-2.6289</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2705</v>
+        <v>-3.2298</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8961</v>
+        <v>0.6009</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7793</v>
+        <v>-4.0223</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6936</v>
+        <v>-2.2483</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0857</v>
+        <v>-1.7741</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5825</v>
+        <v>-2.7379</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.623</v>
+        <v>-1.3524</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>-1.3855</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1969</v>
+        <v>-1.2844</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0706</v>
+        <v>-0.8959</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1262</v>
+        <v>-0.3885</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9749</v>
+        <v>1.9499</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9749</v>
+        <v>1.9499</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3798</v>
+        <v>-0.3441</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2618</v>
+        <v>-0.4918</v>
       </c>
       <c r="U20" t="n">
-        <v>0.118</v>
+        <v>0.1477</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2123</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2123</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2808</v>
+        <v>-2.7818</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5687</v>
+        <v>-1.8396</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7121</v>
+        <v>-0.9422</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9698</v>
+        <v>-1.9581</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0023</v>
+        <v>-2.8411</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0325</v>
+        <v>0.883</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4099</v>
+        <v>-0.2589</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1064</v>
+        <v>-1.6765</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6965</v>
+        <v>1.4176</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5599</v>
+        <v>-1.6991</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8959</v>
+        <v>-1.1646</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.664</v>
+        <v>-0.5345</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7799</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1699</v>
+        <v>1.9499</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6052</v>
+        <v>0.6086</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4291</v>
+        <v>0.3692</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1762</v>
+        <v>0.2394</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0741</v>
+        <v>-1.4323</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.146</v>
+        <v>-1.4323</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. SUAREZ CUSTODIO</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6289</v>
+        <v>-5.9402</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2298</v>
+        <v>-3.8226</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6009</v>
+        <v>-2.1176</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0223</v>
+        <v>-1.5899</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2483</v>
+        <v>-1.3064</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7741</v>
+        <v>-0.2835</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.7379</v>
+        <v>-1.178</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3524</v>
+        <v>-0.619</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3855</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2844</v>
+        <v>-0.4119</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8959</v>
+        <v>-0.6874</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3885</v>
+        <v>0.2755</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9499</v>
+        <v>-0.585</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9499</v>
+        <v>1.3649</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3441</v>
+        <v>-0.7681</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4918</v>
+        <v>-0.6948</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1477</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2123</v>
+        <v>-2.9972</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2123</v>
+        <v>-2.9972</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9968</v>
+        <v>-7.0316</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0546</v>
+        <v>-4.947</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9422</v>
+        <v>-2.0846</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1731</v>
+        <v>-3.125</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8411</v>
+        <v>-1.3975</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.332</v>
+        <v>-1.7274</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.474</v>
+        <v>-1.1535</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.6765</v>
+        <v>-0.2295</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2025</v>
+        <v>-0.924</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6991</v>
+        <v>-1.9715</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1646</v>
+        <v>-1.1681</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5345</v>
+        <v>-0.8034</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9499</v>
+        <v>-2.9248</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9499</v>
+        <v>2.1448</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6086</v>
+        <v>-0.8721</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3692</v>
+        <v>-0.8688</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2394</v>
+        <v>-0.0034</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4323</v>
+        <v>-2.2546</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4323</v>
+        <v>-2.2546</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,235 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9402</v>
+        <v>-12.8272</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8226</v>
+        <v>-12.126</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1176</v>
+        <v>-0.7012</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5899</v>
+        <v>-10.6024</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3064</v>
+        <v>-11.2501</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2835</v>
+        <v>0.6474999999999997</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.178</v>
+        <v>-3.4741</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.619</v>
+        <v>-4.7034</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5590000000000001</v>
+        <v>1.2293</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4119</v>
+        <v>-7.128299999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6874</v>
+        <v>-6.5467</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2755</v>
+        <v>-0.5814999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.585</v>
+        <v>5.849599999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9499</v>
+        <v>-13.6492</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3649</v>
+        <v>19.4985</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7681</v>
+        <v>-4.1217</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6948</v>
+        <v>-1.6604</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-2.4615</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.9972</v>
+        <v>-3.952699999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>6.657500000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.9972</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536138_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C. KNOWLES</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-7.0316</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-4.947</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-2.0846</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-3.125</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-1.3975</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-1.7274</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-1.1535</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-0.2295</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-0.924</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-1.9715</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-1.1681</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-0.8034</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-0.7799</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-2.9248</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.1448</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-0.8721</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-0.8688</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.0034</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-2.2546</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-2.2546</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536138_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-12.8272</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-12.126</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.7012</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-10.6024</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-11.2501</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.6475000000000002</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-3.4742</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-4.7034</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.2292</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-7.1283</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-6.5467</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.5815</v>
-      </c>
-      <c r="P26" t="n">
-        <v>5.849599999999999</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-13.6492</v>
-      </c>
-      <c r="R26" t="n">
-        <v>19.4985</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-4.1217</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-1.6604</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-2.4615</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-3.952699999999999</v>
-      </c>
-      <c r="W26" t="n">
-        <v>6.6575</v>
-      </c>
-      <c r="X26" t="n">
         <v>-10.6101</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
